--- a/database/event/5554/event_5554_evp_summary.xlsx
+++ b/database/event/5554/event_5554_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.4751</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E2" t="n">
         <v>6.4635</v>
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>13.3498</v>
+        <v>12.528</v>
       </c>
       <c r="I2" t="n">
         <v>14.4464</v>
@@ -538,7 +538,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -548,7 +548,7 @@
         <v>4.4751</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E3" t="n">
         <v>6.4635</v>
@@ -560,71 +560,71 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.8774</v>
+        <v>10.9218</v>
       </c>
       <c r="I3" t="n">
-        <v>8.3675</v>
+        <v>12.3849</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>475</v>
+        <v>535</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>8.3675</v>
+        <v>12.3849</v>
       </c>
       <c r="N3" t="n">
-        <v>475</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4635</v>
+        <v>6.2544</v>
       </c>
       <c r="C4" t="n">
-        <v>4.4751</v>
+        <v>4.3303</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1897</v>
+        <v>2.0478</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4635</v>
+        <v>6.2544</v>
       </c>
       <c r="F4" t="n">
-        <v>6.4635</v>
+        <v>6.2544</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>11.5516</v>
+        <v>7.5037</v>
       </c>
       <c r="I4" t="n">
-        <v>12.3849</v>
+        <v>8.3675</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>535</v>
+        <v>475</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>12.3849</v>
+        <v>8.3675</v>
       </c>
       <c r="N4" t="n">
-        <v>535</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5">
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7483</v>
+        <v>5.6067</v>
       </c>
       <c r="C5" t="n">
-        <v>3.9799</v>
+        <v>3.8819</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9008</v>
+        <v>1.7898</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7483</v>
+        <v>5.6067</v>
       </c>
       <c r="F5" t="n">
-        <v>5.7483</v>
+        <v>5.6067</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7102</v>
+        <v>6.4882</v>
       </c>
       <c r="I5" t="n">
         <v>6.9966</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.5783</v>
+        <v>5.4203</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8622</v>
+        <v>3.7528</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8321</v>
+        <v>1.7155</v>
       </c>
       <c r="E6" t="n">
-        <v>5.5783</v>
+        <v>5.4203</v>
       </c>
       <c r="F6" t="n">
-        <v>5.5783</v>
+        <v>5.4203</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>6.4437</v>
+        <v>6.196</v>
       </c>
       <c r="I6" t="n">
-        <v>6.813</v>
+        <v>6.6257</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>461</v>
+        <v>350</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6.813</v>
+        <v>6.6257</v>
       </c>
       <c r="N6" t="n">
-        <v>461</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.5403</v>
+        <v>5.3981</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8359</v>
+        <v>3.7375</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8168</v>
+        <v>1.7067</v>
       </c>
       <c r="E7" t="n">
-        <v>5.5403</v>
+        <v>5.3981</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5403</v>
+        <v>5.3981</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>6.3841</v>
+        <v>6.1611</v>
       </c>
       <c r="I7" t="n">
-        <v>6.6257</v>
+        <v>6.813</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>350</v>
+        <v>461</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6.6257</v>
+        <v>6.813</v>
       </c>
       <c r="N7" t="n">
-        <v>350</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8">
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.5127</v>
+        <v>5.3789</v>
       </c>
       <c r="C8" t="n">
-        <v>3.8168</v>
+        <v>3.7242</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8056</v>
+        <v>1.699</v>
       </c>
       <c r="E8" t="n">
-        <v>5.5127</v>
+        <v>5.3789</v>
       </c>
       <c r="F8" t="n">
-        <v>5.5127</v>
+        <v>5.3789</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>6.3408</v>
+        <v>6.131</v>
       </c>
       <c r="I8" t="n">
         <v>6.6114</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.4539</v>
+        <v>5.2791</v>
       </c>
       <c r="C9" t="n">
-        <v>3.7761</v>
+        <v>3.6551</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7819</v>
+        <v>1.6593</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4539</v>
+        <v>5.2791</v>
       </c>
       <c r="F9" t="n">
-        <v>5.4539</v>
+        <v>5.2791</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>6.2487</v>
+        <v>5.9746</v>
       </c>
       <c r="I9" t="n">
         <v>6.6067</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.4271</v>
+        <v>5.2113</v>
       </c>
       <c r="C10" t="n">
-        <v>3.7576</v>
+        <v>3.6081</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7711</v>
+        <v>1.6323</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4271</v>
+        <v>5.2113</v>
       </c>
       <c r="F10" t="n">
-        <v>5.4271</v>
+        <v>5.2113</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>6.2067</v>
+        <v>5.8683</v>
       </c>
       <c r="I10" t="n">
         <v>6.6544</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.3659</v>
+        <v>5.1949</v>
       </c>
       <c r="C11" t="n">
-        <v>3.7152</v>
+        <v>3.5968</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7463</v>
+        <v>1.6257</v>
       </c>
       <c r="E11" t="n">
-        <v>5.3659</v>
+        <v>5.1949</v>
       </c>
       <c r="F11" t="n">
-        <v>5.3659</v>
+        <v>5.1949</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.1106</v>
+        <v>5.8426</v>
       </c>
       <c r="I11" t="n">
         <v>6.4608</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.254</v>
+        <v>5.1425</v>
       </c>
       <c r="C12" t="n">
-        <v>3.6377</v>
+        <v>3.5605</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7011</v>
+        <v>1.6049</v>
       </c>
       <c r="E12" t="n">
-        <v>5.254</v>
+        <v>5.1425</v>
       </c>
       <c r="F12" t="n">
-        <v>5.254</v>
+        <v>5.1425</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5.9351</v>
+        <v>5.7603</v>
       </c>
       <c r="I12" t="n">
         <v>6.1598</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.212</v>
+        <v>5.0345</v>
       </c>
       <c r="C13" t="n">
-        <v>3.6086</v>
+        <v>3.4857</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6842</v>
+        <v>1.5618</v>
       </c>
       <c r="E13" t="n">
-        <v>5.212</v>
+        <v>5.0345</v>
       </c>
       <c r="F13" t="n">
-        <v>5.212</v>
+        <v>5.0345</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8693</v>
+        <v>5.591</v>
       </c>
       <c r="I13" t="n">
         <v>6.2345</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.0828</v>
+        <v>4.9632</v>
       </c>
       <c r="C14" t="n">
-        <v>3.5192</v>
+        <v>3.4364</v>
       </c>
       <c r="D14" t="n">
-        <v>1.632</v>
+        <v>1.5334</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0828</v>
+        <v>4.9632</v>
       </c>
       <c r="F14" t="n">
-        <v>5.0828</v>
+        <v>4.9632</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6667</v>
+        <v>5.4793</v>
       </c>
       <c r="I14" t="n">
         <v>5.9086</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.0506</v>
+        <v>4.9451</v>
       </c>
       <c r="C15" t="n">
-        <v>3.4969</v>
+        <v>3.4238</v>
       </c>
       <c r="D15" t="n">
-        <v>1.619</v>
+        <v>1.5262</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0506</v>
+        <v>4.9451</v>
       </c>
       <c r="F15" t="n">
-        <v>5.0506</v>
+        <v>4.9451</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>5.6163</v>
+        <v>5.4508</v>
       </c>
       <c r="I15" t="n">
         <v>5.8288</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.9424</v>
+        <v>4.8781</v>
       </c>
       <c r="C16" t="n">
-        <v>3.422</v>
+        <v>3.3774</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5753</v>
+        <v>1.4995</v>
       </c>
       <c r="E16" t="n">
-        <v>4.9424</v>
+        <v>4.8781</v>
       </c>
       <c r="F16" t="n">
-        <v>4.9424</v>
+        <v>4.8781</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4466</v>
+        <v>5.3458</v>
       </c>
       <c r="I16" t="n">
         <v>5.5745</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.9079</v>
+        <v>4.8066</v>
       </c>
       <c r="C17" t="n">
-        <v>3.3981</v>
+        <v>3.3279</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5613</v>
+        <v>1.471</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9079</v>
+        <v>4.8066</v>
       </c>
       <c r="F17" t="n">
-        <v>4.9079</v>
+        <v>4.8066</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5.3926</v>
+        <v>5.2337</v>
       </c>
       <c r="I17" t="n">
         <v>5.5967</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.4214</v>
+        <v>4.2919</v>
       </c>
       <c r="C18" t="n">
-        <v>3.0612</v>
+        <v>2.9716</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3648</v>
+        <v>1.266</v>
       </c>
       <c r="E18" t="n">
-        <v>4.4214</v>
+        <v>4.2919</v>
       </c>
       <c r="F18" t="n">
-        <v>4.4214</v>
+        <v>4.2919</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6298</v>
+        <v>4.4267</v>
       </c>
       <c r="I18" t="n">
         <v>4.8951</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.3939</v>
+        <v>4.2656</v>
       </c>
       <c r="C19" t="n">
-        <v>3.0422</v>
+        <v>2.9534</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3537</v>
+        <v>1.2555</v>
       </c>
       <c r="E19" t="n">
-        <v>4.3939</v>
+        <v>4.2656</v>
       </c>
       <c r="F19" t="n">
-        <v>4.3939</v>
+        <v>4.2656</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5865</v>
+        <v>4.3853</v>
       </c>
       <c r="I19" t="n">
         <v>4.8493</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.2266</v>
+        <v>4.1354</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9264</v>
+        <v>2.8632</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2861</v>
+        <v>1.2036</v>
       </c>
       <c r="E20" t="n">
-        <v>4.2266</v>
+        <v>4.1354</v>
       </c>
       <c r="F20" t="n">
-        <v>4.2266</v>
+        <v>4.1354</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3243</v>
+        <v>4.1813</v>
       </c>
       <c r="I20" t="n">
         <v>4.5089</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.1593</v>
+        <v>4.0493</v>
       </c>
       <c r="C21" t="n">
-        <v>2.8798</v>
+        <v>2.8036</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2589</v>
+        <v>1.1693</v>
       </c>
       <c r="E21" t="n">
-        <v>4.1593</v>
+        <v>4.0493</v>
       </c>
       <c r="F21" t="n">
-        <v>4.1593</v>
+        <v>4.0493</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2187</v>
+        <v>4.0493</v>
       </c>
       <c r="I21" t="n">
-        <v>4.4812</v>
+        <v>4.3301</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>475</v>
+        <v>350</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.4812</v>
+        <v>4.3301</v>
       </c>
       <c r="N21" t="n">
-        <v>475</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.1296</v>
+        <v>4.0186</v>
       </c>
       <c r="C22" t="n">
-        <v>2.8592</v>
+        <v>2.7824</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2469</v>
+        <v>1.1571</v>
       </c>
       <c r="E22" t="n">
-        <v>4.1296</v>
+        <v>4.0186</v>
       </c>
       <c r="F22" t="n">
-        <v>4.1296</v>
+        <v>4.0186</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1722</v>
+        <v>4.0186</v>
       </c>
       <c r="I22" t="n">
-        <v>4.3301</v>
+        <v>4.4812</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>350</v>
+        <v>475</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.3301</v>
+        <v>4.4812</v>
       </c>
       <c r="N22" t="n">
-        <v>350</v>
+        <v>475</v>
       </c>
     </row>
     <row r="23">
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.0317</v>
+        <v>3.9867</v>
       </c>
       <c r="C23" t="n">
-        <v>2.7914</v>
+        <v>2.7603</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2074</v>
+        <v>1.1444</v>
       </c>
       <c r="E23" t="n">
-        <v>4.0317</v>
+        <v>3.9867</v>
       </c>
       <c r="F23" t="n">
-        <v>4.0317</v>
+        <v>3.9867</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4.0317</v>
+        <v>3.9867</v>
       </c>
       <c r="I23" t="n">
         <v>4.0882</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.9076</v>
+        <v>3.8209</v>
       </c>
       <c r="C24" t="n">
-        <v>2.7055</v>
+        <v>2.6455</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1572</v>
+        <v>1.0783</v>
       </c>
       <c r="E24" t="n">
-        <v>3.9076</v>
+        <v>3.8209</v>
       </c>
       <c r="F24" t="n">
-        <v>3.9076</v>
+        <v>3.8209</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3.9076</v>
+        <v>3.8209</v>
       </c>
       <c r="I24" t="n">
         <v>4.018</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.7645</v>
+        <v>3.6536</v>
       </c>
       <c r="C25" t="n">
-        <v>2.6064</v>
+        <v>2.5296</v>
       </c>
       <c r="D25" t="n">
-        <v>1.0994</v>
+        <v>1.0117</v>
       </c>
       <c r="E25" t="n">
-        <v>3.7645</v>
+        <v>3.6536</v>
       </c>
       <c r="F25" t="n">
-        <v>3.7645</v>
+        <v>3.6536</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.7645</v>
+        <v>3.6536</v>
       </c>
       <c r="I25" t="n">
         <v>3.907</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.6096</v>
+        <v>3.4384</v>
       </c>
       <c r="C26" t="n">
-        <v>2.4992</v>
+        <v>2.3806</v>
       </c>
       <c r="D26" t="n">
-        <v>1.0368</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>3.6096</v>
+        <v>3.4384</v>
       </c>
       <c r="F26" t="n">
-        <v>3.6096</v>
+        <v>3.4384</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6096</v>
+        <v>3.4384</v>
       </c>
       <c r="I26" t="n">
         <v>3.8342</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.512</v>
+        <v>3.4341</v>
       </c>
       <c r="C27" t="n">
-        <v>2.4316</v>
+        <v>2.3777</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9974</v>
+        <v>0.9242</v>
       </c>
       <c r="E27" t="n">
-        <v>3.512</v>
+        <v>3.4341</v>
       </c>
       <c r="F27" t="n">
-        <v>3.512</v>
+        <v>3.4341</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3.512</v>
+        <v>3.4341</v>
       </c>
       <c r="I27" t="n">
         <v>3.6112</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>doto</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.4139</v>
+        <v>3.3357</v>
       </c>
       <c r="C28" t="n">
-        <v>2.3637</v>
+        <v>2.3095</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9578</v>
+        <v>0.885</v>
       </c>
       <c r="E28" t="n">
-        <v>3.4139</v>
+        <v>3.3357</v>
       </c>
       <c r="F28" t="n">
-        <v>3.4139</v>
+        <v>3.3357</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.4139</v>
+        <v>3.3357</v>
       </c>
       <c r="I28" t="n">
-        <v>3.5596</v>
+        <v>3.5078</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5596</v>
+        <v>3.5078</v>
       </c>
       <c r="N28" t="n">
-        <v>369</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>doto</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.4114</v>
+        <v>3.3009</v>
       </c>
       <c r="C29" t="n">
-        <v>2.3619</v>
+        <v>2.2854</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9568</v>
+        <v>0.8712</v>
       </c>
       <c r="E29" t="n">
-        <v>3.4114</v>
+        <v>3.3009</v>
       </c>
       <c r="F29" t="n">
-        <v>3.4114</v>
+        <v>3.3009</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3.4114</v>
+        <v>3.3009</v>
       </c>
       <c r="I29" t="n">
-        <v>3.5078</v>
+        <v>3.5596</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>320</v>
+        <v>369</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5078</v>
+        <v>3.5596</v>
       </c>
       <c r="N29" t="n">
-        <v>320</v>
+        <v>369</v>
       </c>
     </row>
     <row r="30">
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.4034</v>
+        <v>3.2908</v>
       </c>
       <c r="C30" t="n">
-        <v>2.3564</v>
+        <v>2.2784</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9535</v>
+        <v>0.8671</v>
       </c>
       <c r="E30" t="n">
-        <v>3.4034</v>
+        <v>3.2908</v>
       </c>
       <c r="F30" t="n">
-        <v>3.4034</v>
+        <v>3.2908</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3.4034</v>
+        <v>3.2908</v>
       </c>
       <c r="I30" t="n">
         <v>3.5486</v>
@@ -1826,277 +1826,277 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.2542</v>
+        <v>3.1643</v>
       </c>
       <c r="C31" t="n">
-        <v>2.2531</v>
+        <v>2.1909</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8933</v>
+        <v>0.8167</v>
       </c>
       <c r="E31" t="n">
-        <v>3.2542</v>
+        <v>3.1643</v>
       </c>
       <c r="F31" t="n">
-        <v>3.2542</v>
+        <v>3.1643</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2542</v>
+        <v>3.1643</v>
       </c>
       <c r="I31" t="n">
-        <v>3.4567</v>
+        <v>3.3275</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>475</v>
+        <v>344</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4567</v>
+        <v>3.3275</v>
       </c>
       <c r="N31" t="n">
-        <v>475</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.2361</v>
+        <v>3.0999</v>
       </c>
       <c r="C32" t="n">
-        <v>2.2406</v>
+        <v>2.1463</v>
       </c>
       <c r="D32" t="n">
-        <v>0.886</v>
+        <v>0.7911</v>
       </c>
       <c r="E32" t="n">
-        <v>3.2361</v>
+        <v>3.0999</v>
       </c>
       <c r="F32" t="n">
-        <v>3.2361</v>
+        <v>3.0999</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3.2361</v>
+        <v>3.0999</v>
       </c>
       <c r="I32" t="n">
-        <v>3.3275</v>
+        <v>3.4567</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>344</v>
+        <v>475</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3275</v>
+        <v>3.4567</v>
       </c>
       <c r="N32" t="n">
-        <v>344</v>
+        <v>475</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.1838</v>
+        <v>3.0534</v>
       </c>
       <c r="C33" t="n">
-        <v>2.2044</v>
+        <v>2.1141</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8648</v>
+        <v>0.7726</v>
       </c>
       <c r="E33" t="n">
-        <v>3.1838</v>
+        <v>3.0534</v>
       </c>
       <c r="F33" t="n">
-        <v>3.1838</v>
+        <v>3.0534</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3.1838</v>
+        <v>3.0534</v>
       </c>
       <c r="I33" t="n">
-        <v>3.4453</v>
+        <v>3.2109</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>619</v>
+        <v>320</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4453</v>
+        <v>3.2109</v>
       </c>
       <c r="N33" t="n">
-        <v>619</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Bymas</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.138</v>
+        <v>3.0226</v>
       </c>
       <c r="C34" t="n">
-        <v>2.1727</v>
+        <v>2.0928</v>
       </c>
       <c r="D34" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7603</v>
       </c>
       <c r="E34" t="n">
-        <v>3.138</v>
+        <v>3.0226</v>
       </c>
       <c r="F34" t="n">
-        <v>3.138</v>
+        <v>3.0226</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.138</v>
+        <v>3.0226</v>
       </c>
       <c r="I34" t="n">
-        <v>3.3179</v>
+        <v>3.2322</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>488</v>
+        <v>392</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3179</v>
+        <v>3.2322</v>
       </c>
       <c r="N34" t="n">
-        <v>488</v>
+        <v>392</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.1227</v>
+        <v>3.0004</v>
       </c>
       <c r="C35" t="n">
-        <v>2.1621</v>
+        <v>2.0774</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8401</v>
+        <v>0.7514</v>
       </c>
       <c r="E35" t="n">
-        <v>3.1227</v>
+        <v>3.0004</v>
       </c>
       <c r="F35" t="n">
-        <v>3.1227</v>
+        <v>3.0004</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>3.1227</v>
+        <v>3.0004</v>
       </c>
       <c r="I35" t="n">
-        <v>3.2109</v>
+        <v>3.3179</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>320</v>
+        <v>488</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2109</v>
+        <v>3.3179</v>
       </c>
       <c r="N35" t="n">
-        <v>320</v>
+        <v>488</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bymas</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.1143</v>
+        <v>2.9878</v>
       </c>
       <c r="C36" t="n">
-        <v>2.1562</v>
+        <v>2.0687</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8367</v>
+        <v>0.7464</v>
       </c>
       <c r="E36" t="n">
-        <v>3.1143</v>
+        <v>2.9878</v>
       </c>
       <c r="F36" t="n">
-        <v>3.1143</v>
+        <v>2.9878</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3.1143</v>
+        <v>2.9878</v>
       </c>
       <c r="I36" t="n">
-        <v>3.2322</v>
+        <v>3.4453</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>392</v>
+        <v>619</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2322</v>
+        <v>3.4453</v>
       </c>
       <c r="N36" t="n">
-        <v>392</v>
+        <v>619</v>
       </c>
     </row>
     <row r="37">
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.8737</v>
+        <v>2.81</v>
       </c>
       <c r="C37" t="n">
-        <v>1.9897</v>
+        <v>1.9456</v>
       </c>
       <c r="D37" t="n">
-        <v>0.7395</v>
+        <v>0.6756</v>
       </c>
       <c r="E37" t="n">
-        <v>2.8737</v>
+        <v>2.81</v>
       </c>
       <c r="F37" t="n">
-        <v>2.8737</v>
+        <v>2.81</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.8737</v>
+        <v>2.81</v>
       </c>
       <c r="I37" t="n">
         <v>2.9549</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.7619</v>
+        <v>2.6705</v>
       </c>
       <c r="C38" t="n">
-        <v>1.9123</v>
+        <v>1.849</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6944</v>
+        <v>0.62</v>
       </c>
       <c r="E38" t="n">
-        <v>2.7619</v>
+        <v>2.6705</v>
       </c>
       <c r="F38" t="n">
-        <v>2.7619</v>
+        <v>2.6705</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2.7619</v>
+        <v>2.6705</v>
       </c>
       <c r="I38" t="n">
         <v>2.8798</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.7026</v>
+        <v>2.6436</v>
       </c>
       <c r="C39" t="n">
-        <v>1.8712</v>
+        <v>1.8303</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6704</v>
+        <v>0.6093</v>
       </c>
       <c r="E39" t="n">
-        <v>2.7026</v>
+        <v>2.6436</v>
       </c>
       <c r="F39" t="n">
-        <v>2.7026</v>
+        <v>2.6436</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.7026</v>
+        <v>2.6436</v>
       </c>
       <c r="I39" t="n">
-        <v>2.8311</v>
+        <v>2.7337</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>457</v>
+        <v>271</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.8311</v>
+        <v>2.7337</v>
       </c>
       <c r="N39" t="n">
-        <v>457</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.6834</v>
+        <v>2.6035</v>
       </c>
       <c r="C40" t="n">
-        <v>1.8579</v>
+        <v>1.8026</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6627</v>
+        <v>0.5933</v>
       </c>
       <c r="E40" t="n">
-        <v>2.6834</v>
+        <v>2.6035</v>
       </c>
       <c r="F40" t="n">
-        <v>2.6834</v>
+        <v>2.6035</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2.6834</v>
+        <v>2.6035</v>
       </c>
       <c r="I40" t="n">
-        <v>2.7337</v>
+        <v>2.8311</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>271</v>
+        <v>457</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.7337</v>
+        <v>2.8311</v>
       </c>
       <c r="N40" t="n">
-        <v>271</v>
+        <v>457</v>
       </c>
     </row>
     <row r="41">
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.66</v>
+        <v>2.601</v>
       </c>
       <c r="C41" t="n">
-        <v>1.8417</v>
+        <v>1.8008</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6532</v>
+        <v>0.5923</v>
       </c>
       <c r="E41" t="n">
-        <v>2.66</v>
+        <v>2.601</v>
       </c>
       <c r="F41" t="n">
-        <v>2.66</v>
+        <v>2.601</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.66</v>
+        <v>2.601</v>
       </c>
       <c r="I41" t="n">
         <v>2.7351</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.6291</v>
+        <v>2.5901</v>
       </c>
       <c r="C42" t="n">
-        <v>1.8203</v>
+        <v>1.7933</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6407</v>
+        <v>0.588</v>
       </c>
       <c r="E42" t="n">
-        <v>2.6291</v>
+        <v>2.5901</v>
       </c>
       <c r="F42" t="n">
-        <v>2.6291</v>
+        <v>2.5901</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.6291</v>
+        <v>2.5901</v>
       </c>
       <c r="I42" t="n">
         <v>2.6784</v>
@@ -2378,78 +2378,78 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.6019</v>
+        <v>2.4738</v>
       </c>
       <c r="C43" t="n">
-        <v>1.8015</v>
+        <v>1.7128</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6297</v>
+        <v>0.5417</v>
       </c>
       <c r="E43" t="n">
-        <v>2.6019</v>
+        <v>2.4738</v>
       </c>
       <c r="F43" t="n">
-        <v>2.6019</v>
+        <v>2.4738</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2.6019</v>
+        <v>2.4738</v>
       </c>
       <c r="I43" t="n">
-        <v>2.7896</v>
+        <v>2.6014</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>535</v>
+        <v>395</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.7896</v>
+        <v>2.6014</v>
       </c>
       <c r="N43" t="n">
-        <v>535</v>
+        <v>395</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.5928</v>
+        <v>2.4601</v>
       </c>
       <c r="C44" t="n">
-        <v>1.7952</v>
+        <v>1.7033</v>
       </c>
       <c r="D44" t="n">
-        <v>0.6261</v>
+        <v>0.5362</v>
       </c>
       <c r="E44" t="n">
-        <v>2.5928</v>
+        <v>2.4601</v>
       </c>
       <c r="F44" t="n">
-        <v>2.5928</v>
+        <v>2.4601</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2.5928</v>
+        <v>2.4601</v>
       </c>
       <c r="I44" t="n">
-        <v>2.7799</v>
+        <v>2.7896</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.7799</v>
+        <v>2.7896</v>
       </c>
       <c r="N44" t="n">
         <v>535</v>
@@ -2470,47 +2470,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.5299</v>
+        <v>2.4515</v>
       </c>
       <c r="C45" t="n">
-        <v>1.7516</v>
+        <v>1.6973</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6007</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>2.5299</v>
+        <v>2.4515</v>
       </c>
       <c r="F45" t="n">
-        <v>2.5299</v>
+        <v>2.4515</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.5299</v>
+        <v>2.4515</v>
       </c>
       <c r="I45" t="n">
-        <v>2.6014</v>
+        <v>2.7799</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>395</v>
+        <v>535</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.6014</v>
+        <v>2.7799</v>
       </c>
       <c r="N45" t="n">
-        <v>395</v>
+        <v>535</v>
       </c>
     </row>
     <row r="46">
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.3382</v>
+        <v>2.2949</v>
       </c>
       <c r="C46" t="n">
-        <v>1.6189</v>
+        <v>1.5889</v>
       </c>
       <c r="D46" t="n">
-        <v>0.5232</v>
+        <v>0.4704</v>
       </c>
       <c r="E46" t="n">
-        <v>2.3382</v>
+        <v>2.2949</v>
       </c>
       <c r="F46" t="n">
-        <v>2.3382</v>
+        <v>2.2949</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.3382</v>
+        <v>2.2949</v>
       </c>
       <c r="I46" t="n">
         <v>2.3931</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.3191</v>
+        <v>2.2508</v>
       </c>
       <c r="C47" t="n">
-        <v>1.6057</v>
+        <v>1.5584</v>
       </c>
       <c r="D47" t="n">
-        <v>0.5155</v>
+        <v>0.4528</v>
       </c>
       <c r="E47" t="n">
-        <v>2.3191</v>
+        <v>2.2508</v>
       </c>
       <c r="F47" t="n">
-        <v>2.3191</v>
+        <v>2.2508</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2.3191</v>
+        <v>2.2508</v>
       </c>
       <c r="I47" t="n">
         <v>2.4069</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.2362</v>
+        <v>2.1867</v>
       </c>
       <c r="C48" t="n">
-        <v>1.5483</v>
+        <v>1.514</v>
       </c>
       <c r="D48" t="n">
-        <v>0.482</v>
+        <v>0.4273</v>
       </c>
       <c r="E48" t="n">
-        <v>2.2362</v>
+        <v>2.1867</v>
       </c>
       <c r="F48" t="n">
-        <v>2.2362</v>
+        <v>2.1867</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>2.2362</v>
+        <v>2.1867</v>
       </c>
       <c r="I48" t="n">
         <v>2.2994</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.1914</v>
+        <v>2.111</v>
       </c>
       <c r="C49" t="n">
-        <v>1.5173</v>
+        <v>1.4616</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4639</v>
+        <v>0.3971</v>
       </c>
       <c r="E49" t="n">
-        <v>2.1914</v>
+        <v>2.111</v>
       </c>
       <c r="F49" t="n">
-        <v>2.1914</v>
+        <v>2.111</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2.1914</v>
+        <v>2.111</v>
       </c>
       <c r="I49" t="n">
         <v>2.2955</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.037</v>
+        <v>1.9476</v>
       </c>
       <c r="C50" t="n">
-        <v>1.4104</v>
+        <v>1.3485</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4015</v>
+        <v>0.332</v>
       </c>
       <c r="E50" t="n">
-        <v>2.037</v>
+        <v>1.9476</v>
       </c>
       <c r="F50" t="n">
-        <v>2.037</v>
+        <v>1.9476</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2.037</v>
+        <v>1.9476</v>
       </c>
       <c r="I50" t="n">
         <v>2.1537</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.9551</v>
+        <v>1.9189</v>
       </c>
       <c r="C51" t="n">
-        <v>1.3536</v>
+        <v>1.3286</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3685</v>
+        <v>0.3206</v>
       </c>
       <c r="E51" t="n">
-        <v>1.9551</v>
+        <v>1.9189</v>
       </c>
       <c r="F51" t="n">
-        <v>1.9551</v>
+        <v>1.9189</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.9551</v>
+        <v>1.9189</v>
       </c>
       <c r="I51" t="n">
         <v>2.001</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.8959</v>
+        <v>1.8677</v>
       </c>
       <c r="C52" t="n">
-        <v>1.3127</v>
+        <v>1.2931</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3445</v>
+        <v>0.3002</v>
       </c>
       <c r="E52" t="n">
-        <v>1.8959</v>
+        <v>1.8677</v>
       </c>
       <c r="F52" t="n">
-        <v>1.8959</v>
+        <v>1.8677</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.8959</v>
+        <v>1.8677</v>
       </c>
       <c r="I52" t="n">
         <v>1.9314</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.7833</v>
+        <v>1.7568</v>
       </c>
       <c r="C53" t="n">
-        <v>1.2347</v>
+        <v>1.2164</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2991</v>
+        <v>0.256</v>
       </c>
       <c r="E53" t="n">
-        <v>1.7833</v>
+        <v>1.7568</v>
       </c>
       <c r="F53" t="n">
-        <v>1.7833</v>
+        <v>1.7568</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.7833</v>
+        <v>1.7568</v>
       </c>
       <c r="I53" t="n">
         <v>1.8167</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.6667</v>
+        <v>1.6419</v>
       </c>
       <c r="C54" t="n">
-        <v>1.154</v>
+        <v>1.1368</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2519</v>
+        <v>0.2102</v>
       </c>
       <c r="E54" t="n">
-        <v>1.6667</v>
+        <v>1.6419</v>
       </c>
       <c r="F54" t="n">
-        <v>1.6667</v>
+        <v>1.6419</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1.6667</v>
+        <v>1.6419</v>
       </c>
       <c r="I54" t="n">
         <v>1.6979</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.6097</v>
+        <v>1.5858</v>
       </c>
       <c r="C55" t="n">
-        <v>1.1145</v>
+        <v>1.098</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2289</v>
+        <v>0.1879</v>
       </c>
       <c r="E55" t="n">
-        <v>1.6097</v>
+        <v>1.5858</v>
       </c>
       <c r="F55" t="n">
-        <v>1.6097</v>
+        <v>1.5858</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1.6097</v>
+        <v>1.5858</v>
       </c>
       <c r="I55" t="n">
         <v>1.6399</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.5962</v>
+        <v>1.5725</v>
       </c>
       <c r="C56" t="n">
-        <v>1.1052</v>
+        <v>1.0887</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2235</v>
+        <v>0.1826</v>
       </c>
       <c r="E56" t="n">
-        <v>1.5962</v>
+        <v>1.5725</v>
       </c>
       <c r="F56" t="n">
-        <v>1.5962</v>
+        <v>1.5725</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1.5962</v>
+        <v>1.5725</v>
       </c>
       <c r="I56" t="n">
         <v>1.6261</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.5851</v>
+        <v>1.5269</v>
       </c>
       <c r="C57" t="n">
-        <v>1.0975</v>
+        <v>1.0572</v>
       </c>
       <c r="D57" t="n">
-        <v>0.219</v>
+        <v>0.1644</v>
       </c>
       <c r="E57" t="n">
-        <v>1.5851</v>
+        <v>1.5269</v>
       </c>
       <c r="F57" t="n">
-        <v>1.5851</v>
+        <v>1.5269</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1.5851</v>
+        <v>1.5269</v>
       </c>
       <c r="I57" t="n">
         <v>1.6604</v>
@@ -3068,93 +3068,93 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>El1an</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.5517</v>
+        <v>1.5136</v>
       </c>
       <c r="C58" t="n">
-        <v>1.0743</v>
+        <v>1.048</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2055</v>
+        <v>0.1591</v>
       </c>
       <c r="E58" t="n">
-        <v>1.5517</v>
+        <v>1.5136</v>
       </c>
       <c r="F58" t="n">
-        <v>1.5517</v>
+        <v>1.5136</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1.5517</v>
+        <v>1.5136</v>
       </c>
       <c r="I58" t="n">
-        <v>1.6104</v>
+        <v>1.5652</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>350</v>
+        <v>268</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1.6104</v>
+        <v>1.5652</v>
       </c>
       <c r="N58" t="n">
-        <v>350</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>El1an</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.5364</v>
+        <v>1.506</v>
       </c>
       <c r="C59" t="n">
-        <v>1.0638</v>
+        <v>1.0427</v>
       </c>
       <c r="D59" t="n">
-        <v>0.1993</v>
+        <v>0.1561</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5364</v>
+        <v>1.506</v>
       </c>
       <c r="F59" t="n">
-        <v>1.5364</v>
+        <v>1.506</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.5364</v>
+        <v>1.506</v>
       </c>
       <c r="I59" t="n">
-        <v>1.5652</v>
+        <v>1.6104</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>268</v>
+        <v>350</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1.5652</v>
+        <v>1.6104</v>
       </c>
       <c r="N59" t="n">
-        <v>268</v>
+        <v>350</v>
       </c>
     </row>
     <row r="60">
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.4704</v>
+        <v>1.4271</v>
       </c>
       <c r="C60" t="n">
-        <v>1.0181</v>
+        <v>0.9881</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1726</v>
+        <v>0.1246</v>
       </c>
       <c r="E60" t="n">
-        <v>1.4704</v>
+        <v>1.4271</v>
       </c>
       <c r="F60" t="n">
-        <v>1.4704</v>
+        <v>1.4271</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1.4704</v>
+        <v>1.4271</v>
       </c>
       <c r="I60" t="n">
         <v>1.5261</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.3679</v>
+        <v>1.2837</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.8888</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1312</v>
+        <v>0.0675</v>
       </c>
       <c r="E61" t="n">
-        <v>1.3679</v>
+        <v>1.2837</v>
       </c>
       <c r="F61" t="n">
-        <v>1.3679</v>
+        <v>1.2837</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1.3679</v>
+        <v>1.2837</v>
       </c>
       <c r="I61" t="n">
         <v>1.4803</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.3136</v>
+        <v>1.2749</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9095</v>
+        <v>0.8827</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1093</v>
+        <v>0.064</v>
       </c>
       <c r="E62" t="n">
-        <v>1.3136</v>
+        <v>1.2749</v>
       </c>
       <c r="F62" t="n">
-        <v>1.3136</v>
+        <v>1.2749</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1.3136</v>
+        <v>1.2749</v>
       </c>
       <c r="I62" t="n">
         <v>1.3633</v>
@@ -3298,93 +3298,93 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>oBo</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.2217</v>
+        <v>1.208</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8459</v>
+        <v>0.8364</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0722</v>
+        <v>0.0374</v>
       </c>
       <c r="E63" t="n">
-        <v>1.2217</v>
+        <v>1.208</v>
       </c>
       <c r="F63" t="n">
-        <v>1.2217</v>
+        <v>1.208</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1.2217</v>
+        <v>1.208</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2562</v>
+        <v>1.2182</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>1.2562</v>
+        <v>1.2182</v>
       </c>
       <c r="N63" t="n">
-        <v>320</v>
+        <v>291</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>oBo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1.2126</v>
+        <v>1.1946</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8396</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="D64" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="E64" t="n">
-        <v>1.2126</v>
+        <v>1.1946</v>
       </c>
       <c r="F64" t="n">
-        <v>1.2126</v>
+        <v>1.1946</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1.2126</v>
+        <v>1.1946</v>
       </c>
       <c r="I64" t="n">
-        <v>1.2182</v>
+        <v>1.2562</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>1.2182</v>
+        <v>1.2562</v>
       </c>
       <c r="N64" t="n">
-        <v>291</v>
+        <v>320</v>
       </c>
     </row>
     <row r="65">
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1.1615</v>
+        <v>1.1442</v>
       </c>
       <c r="C65" t="n">
-        <v>0.8042</v>
+        <v>0.7922</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0479</v>
+        <v>0.0119</v>
       </c>
       <c r="E65" t="n">
-        <v>1.1615</v>
+        <v>1.1442</v>
       </c>
       <c r="F65" t="n">
-        <v>1.1615</v>
+        <v>1.1442</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1.1615</v>
+        <v>1.1442</v>
       </c>
       <c r="I65" t="n">
         <v>1.1832</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.1503</v>
+        <v>1.0998</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7964</v>
+        <v>0.7615</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0433</v>
+        <v>-0.0057</v>
       </c>
       <c r="E66" t="n">
-        <v>1.1503</v>
+        <v>1.0998</v>
       </c>
       <c r="F66" t="n">
-        <v>1.1503</v>
+        <v>1.0998</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1.1503</v>
+        <v>1.0998</v>
       </c>
       <c r="I66" t="n">
         <v>1.2162</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1.0969</v>
+        <v>1.0646</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7595</v>
+        <v>0.7371</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0218</v>
+        <v>-0.0198</v>
       </c>
       <c r="E67" t="n">
-        <v>1.0969</v>
+        <v>1.0646</v>
       </c>
       <c r="F67" t="n">
-        <v>1.0969</v>
+        <v>1.0646</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1.0969</v>
+        <v>1.0646</v>
       </c>
       <c r="I67" t="n">
         <v>1.1384</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.9777</v>
+        <v>0.9348</v>
       </c>
       <c r="C68" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.6472</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.0264</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9777</v>
+        <v>0.9348</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9777</v>
+        <v>0.9348</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.9777</v>
+        <v>0.9348</v>
       </c>
       <c r="I68" t="n">
         <v>1.0337</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8854</v>
+        <v>0.8658</v>
       </c>
       <c r="C69" t="n">
-        <v>0.613</v>
+        <v>0.5995</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.099</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8854</v>
+        <v>0.8658</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8854</v>
+        <v>0.8658</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8854</v>
+        <v>0.8658</v>
       </c>
       <c r="I69" t="n">
         <v>0.9104</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7619</v>
+        <v>0.734</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5275</v>
+        <v>0.5082</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.1136</v>
+        <v>-0.1515</v>
       </c>
       <c r="E70" t="n">
-        <v>0.7619</v>
+        <v>0.734</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7619</v>
+        <v>0.734</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.7619</v>
+        <v>0.734</v>
       </c>
       <c r="I70" t="n">
         <v>0.7982</v>
@@ -3666,93 +3666,93 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>SHOCK</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7405</v>
+        <v>0.7249</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5127</v>
+        <v>0.5019</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.1222</v>
+        <v>-0.1551</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7405</v>
+        <v>0.7249</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7405</v>
+        <v>0.7249</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.7405</v>
+        <v>0.7249</v>
       </c>
       <c r="I71" t="n">
-        <v>0.7614</v>
+        <v>0.7497</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0.7614</v>
+        <v>0.7497</v>
       </c>
       <c r="N71" t="n">
-        <v>315</v>
+        <v>374</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SHOCK</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7359</v>
+        <v>0.7241</v>
       </c>
       <c r="C72" t="n">
-        <v>0.5095</v>
+        <v>0.5013</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.1241</v>
+        <v>-0.1554</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7359</v>
+        <v>0.7241</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7359</v>
+        <v>0.7241</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.7359</v>
+        <v>0.7241</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7497</v>
+        <v>0.7614</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>374</v>
+        <v>315</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0.7497</v>
+        <v>0.7614</v>
       </c>
       <c r="N72" t="n">
-        <v>374</v>
+        <v>315</v>
       </c>
     </row>
     <row r="73">
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6846</v>
+        <v>0.6619</v>
       </c>
       <c r="C73" t="n">
-        <v>0.474</v>
+        <v>0.4583</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.1448</v>
+        <v>-0.1802</v>
       </c>
       <c r="E73" t="n">
-        <v>0.6846</v>
+        <v>0.6619</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6846</v>
+        <v>0.6619</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.6846</v>
+        <v>0.6619</v>
       </c>
       <c r="I73" t="n">
         <v>0.7138</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5937</v>
+        <v>0.5849</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4111</v>
+        <v>0.405</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.1815</v>
+        <v>-0.2109</v>
       </c>
       <c r="E74" t="n">
-        <v>0.5937</v>
+        <v>0.5849</v>
       </c>
       <c r="F74" t="n">
-        <v>0.5937</v>
+        <v>0.5849</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.5937</v>
+        <v>0.5849</v>
       </c>
       <c r="I74" t="n">
         <v>0.6048</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5306</v>
+        <v>0.5228</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3674</v>
+        <v>0.362</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.207</v>
+        <v>-0.2356</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5306</v>
+        <v>0.5228</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5306</v>
+        <v>0.5228</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0.5306</v>
+        <v>0.5228</v>
       </c>
       <c r="I75" t="n">
         <v>0.5406</v>
@@ -3906,7 +3906,7 @@
         <v>0.2562</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.2719</v>
+        <v>-0.2965</v>
       </c>
       <c r="E76" t="n">
         <v>0.37</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>NickelBack</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.3383</v>
+        <v>0.3289</v>
       </c>
       <c r="C77" t="n">
-        <v>0.2342</v>
+        <v>0.2277</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.2847</v>
+        <v>-0.3129</v>
       </c>
       <c r="E77" t="n">
-        <v>0.3383</v>
+        <v>0.3289</v>
       </c>
       <c r="F77" t="n">
-        <v>0.3383</v>
+        <v>0.3289</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.3383</v>
+        <v>0.3289</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3627</v>
+        <v>0.3401</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>535</v>
+        <v>268</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0.3627</v>
+        <v>0.3401</v>
       </c>
       <c r="N77" t="n">
-        <v>535</v>
+        <v>268</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NickelBack</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.3338</v>
+        <v>0.3198</v>
       </c>
       <c r="C78" t="n">
-        <v>0.2311</v>
+        <v>0.2214</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.2865</v>
+        <v>-0.3165</v>
       </c>
       <c r="E78" t="n">
-        <v>0.3338</v>
+        <v>0.3198</v>
       </c>
       <c r="F78" t="n">
-        <v>0.3338</v>
+        <v>0.3198</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.3338</v>
+        <v>0.3198</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3401</v>
+        <v>0.3627</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>268</v>
+        <v>535</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0.3401</v>
+        <v>0.3627</v>
       </c>
       <c r="N78" t="n">
-        <v>268</v>
+        <v>535</v>
       </c>
     </row>
     <row r="79">
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.3118</v>
+        <v>0.2926</v>
       </c>
       <c r="C79" t="n">
-        <v>0.2159</v>
+        <v>0.2026</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.2954</v>
+        <v>-0.3273</v>
       </c>
       <c r="E79" t="n">
-        <v>0.3118</v>
+        <v>0.2926</v>
       </c>
       <c r="F79" t="n">
-        <v>0.3118</v>
+        <v>0.2926</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0.3118</v>
+        <v>0.2926</v>
       </c>
       <c r="I79" t="n">
         <v>0.3374</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.307</v>
+        <v>0.2881</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2126</v>
+        <v>0.1995</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.2973</v>
+        <v>-0.3291</v>
       </c>
       <c r="E80" t="n">
-        <v>0.307</v>
+        <v>0.2881</v>
       </c>
       <c r="F80" t="n">
-        <v>0.307</v>
+        <v>0.2881</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.307</v>
+        <v>0.2881</v>
       </c>
       <c r="I80" t="n">
         <v>0.3322</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.1892</v>
+        <v>0.185</v>
       </c>
       <c r="C81" t="n">
-        <v>0.131</v>
+        <v>0.1281</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.3449</v>
+        <v>-0.3702</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1892</v>
+        <v>0.185</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1892</v>
+        <v>0.185</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1892</v>
+        <v>0.185</v>
       </c>
       <c r="I81" t="n">
         <v>0.1945</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.1526</v>
+        <v>0.1504</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1057</v>
+        <v>0.1041</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.3597</v>
+        <v>-0.384</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1526</v>
+        <v>0.1504</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1526</v>
+        <v>0.1504</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1526</v>
+        <v>0.1504</v>
       </c>
       <c r="I82" t="n">
         <v>0.1555</v>
@@ -4222,25 +4222,25 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.0058</v>
+        <v>-0.0057</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.004</v>
+        <v>-0.0039</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.4237</v>
+        <v>-0.4462</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.0058</v>
+        <v>-0.0057</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.0058</v>
+        <v>-0.0057</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.0058</v>
+        <v>-0.0057</v>
       </c>
       <c r="I83" t="n">
         <v>-0.0059</v>
@@ -4268,25 +4268,25 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.0211</v>
+        <v>-0.0204</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.0146</v>
+        <v>-0.0141</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.4299</v>
+        <v>-0.452</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.0211</v>
+        <v>-0.0204</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.0211</v>
+        <v>-0.0204</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.0211</v>
+        <v>-0.0204</v>
       </c>
       <c r="I84" t="n">
         <v>-0.022</v>
@@ -4314,25 +4314,25 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.3197</v>
+        <v>-0.3185</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.2214</v>
+        <v>-0.2205</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.5505</v>
+        <v>-0.5708</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.3197</v>
+        <v>-0.3185</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.3197</v>
+        <v>-0.3185</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.3197</v>
+        <v>-0.3185</v>
       </c>
       <c r="I85" t="n">
         <v>-0.3212</v>
@@ -4360,25 +4360,25 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.353</v>
+        <v>-0.3452</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.2444</v>
+        <v>-0.239</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5814</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.353</v>
+        <v>-0.3452</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.353</v>
+        <v>-0.3452</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.353</v>
+        <v>-0.3452</v>
       </c>
       <c r="I86" t="n">
         <v>-0.363</v>
@@ -4406,25 +4406,25 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.3611</v>
+        <v>-0.3453</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.25</v>
+        <v>-0.2391</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.5672</v>
+        <v>-0.5815</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.3611</v>
+        <v>-0.3453</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.3611</v>
+        <v>-0.3453</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.3611</v>
+        <v>-0.3453</v>
       </c>
       <c r="I87" t="n">
         <v>-0.3818</v>
@@ -4452,25 +4452,25 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.4111</v>
+        <v>-0.402</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.2846</v>
+        <v>-0.2783</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.5874</v>
+        <v>-0.6041</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.4111</v>
+        <v>-0.402</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.4111</v>
+        <v>-0.402</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.4111</v>
+        <v>-0.402</v>
       </c>
       <c r="I88" t="n">
         <v>-0.4227</v>
@@ -4498,25 +4498,25 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.4827</v>
+        <v>-0.4756</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.3342</v>
+        <v>-0.3293</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.6163999999999999</v>
+        <v>-0.6334</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.4827</v>
+        <v>-0.4756</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.4827</v>
+        <v>-0.4756</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.4827</v>
+        <v>-0.4756</v>
       </c>
       <c r="I89" t="n">
         <v>-0.4918</v>
@@ -4544,25 +4544,25 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.6498</v>
+        <v>-0.6354</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.4499</v>
+        <v>-0.4399</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.6839</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.6498</v>
+        <v>-0.6354</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.6498</v>
+        <v>-0.6354</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.6498</v>
+        <v>-0.6354</v>
       </c>
       <c r="I90" t="n">
         <v>-0.6682</v>
@@ -4590,25 +4590,25 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.8171</v>
+        <v>-0.793</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.5657</v>
+        <v>-0.549</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.7598</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.8171</v>
+        <v>-0.793</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.8171</v>
+        <v>-0.793</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.8171</v>
+        <v>-0.793</v>
       </c>
       <c r="I91" t="n">
         <v>-0.848</v>
@@ -4632,93 +4632,93 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.9711</v>
+        <v>-0.9581</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.6724</v>
+        <v>-0.6634</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.8137</v>
+        <v>-0.8256</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.9711</v>
+        <v>-0.9581</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.9711</v>
+        <v>-0.9581</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.9711</v>
+        <v>-0.9581</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.9756</v>
+        <v>-1.0075</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>-0.9756</v>
+        <v>-1.0075</v>
       </c>
       <c r="N92" t="n">
-        <v>291</v>
+        <v>320</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.9798</v>
+        <v>-0.9675</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.6784</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.8172</v>
+        <v>-0.8294</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.9798</v>
+        <v>-0.9675</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.9798</v>
+        <v>-0.9675</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.9798</v>
+        <v>-0.9675</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.0075</v>
+        <v>-0.9756</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>-1.0075</v>
+        <v>-0.9756</v>
       </c>
       <c r="N93" t="n">
-        <v>320</v>
+        <v>291</v>
       </c>
     </row>
     <row r="94">
@@ -4728,25 +4728,25 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-1.0494</v>
+        <v>-1.0262</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.7266</v>
+        <v>-0.7105</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.8527</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.0494</v>
+        <v>-1.0262</v>
       </c>
       <c r="F94" t="n">
-        <v>-1.0494</v>
+        <v>-1.0262</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>-1.0494</v>
+        <v>-1.0262</v>
       </c>
       <c r="I94" t="n">
         <v>-1.0791</v>
@@ -4774,25 +4774,25 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-1.1275</v>
+        <v>-1.1149</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.7806</v>
+        <v>-0.7719</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.8768</v>
+        <v>-0.8881</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.1275</v>
+        <v>-1.1149</v>
       </c>
       <c r="F95" t="n">
-        <v>-1.1275</v>
+        <v>-1.1149</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>-1.1275</v>
+        <v>-1.1149</v>
       </c>
       <c r="I95" t="n">
         <v>-1.1433</v>
@@ -4820,25 +4820,25 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-1.2626</v>
+        <v>-1.2439</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.8742</v>
+        <v>-0.8612</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.9314</v>
+        <v>-0.9395</v>
       </c>
       <c r="E96" t="n">
-        <v>-1.2626</v>
+        <v>-1.2439</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.2626</v>
+        <v>-1.2439</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>-1.2626</v>
+        <v>-1.2439</v>
       </c>
       <c r="I96" t="n">
         <v>-1.2863</v>
@@ -4872,7 +4872,7 @@
         <v>-0.8745000000000001</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.9316</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="E97" t="n">
         <v>-1.263</v>
@@ -4912,25 +4912,25 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-1.3443</v>
+        <v>-1.3145</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.9308</v>
+        <v>-0.9101</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.9644</v>
+        <v>-0.9676</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.3443</v>
+        <v>-1.3145</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.3443</v>
+        <v>-1.3145</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>-1.3443</v>
+        <v>-1.3145</v>
       </c>
       <c r="I98" t="n">
         <v>-1.3823</v>
@@ -4958,25 +4958,25 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-1.421</v>
+        <v>-1.3999</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.9839</v>
+        <v>-0.9692</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.9954</v>
+        <v>-1.0016</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.421</v>
+        <v>-1.3999</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.421</v>
+        <v>-1.3999</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.421</v>
+        <v>-1.3999</v>
       </c>
       <c r="I99" t="n">
         <v>-1.4476</v>
@@ -5010,7 +5010,7 @@
         <v>-1.1156</v>
       </c>
       <c r="D100" t="n">
-        <v>-1.0723</v>
+        <v>-1.0859</v>
       </c>
       <c r="E100" t="n">
         <v>-1.6113</v>
@@ -5056,7 +5056,7 @@
         <v>-1.1168</v>
       </c>
       <c r="D101" t="n">
-        <v>-1.073</v>
+        <v>-1.0865</v>
       </c>
       <c r="E101" t="n">
         <v>-1.613</v>
@@ -5096,25 +5096,25 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-1.687</v>
+        <v>-1.6682</v>
       </c>
       <c r="C102" t="n">
-        <v>-1.168</v>
+        <v>-1.155</v>
       </c>
       <c r="D102" t="n">
-        <v>-1.1029</v>
+        <v>-1.1085</v>
       </c>
       <c r="E102" t="n">
-        <v>-1.687</v>
+        <v>-1.6682</v>
       </c>
       <c r="F102" t="n">
-        <v>-1.687</v>
+        <v>-1.6682</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.687</v>
+        <v>-1.6682</v>
       </c>
       <c r="I102" t="n">
         <v>-1.7107</v>
@@ -5142,25 +5142,25 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-1.9424</v>
+        <v>-1.9351</v>
       </c>
       <c r="C103" t="n">
-        <v>-1.3449</v>
+        <v>-1.3398</v>
       </c>
       <c r="D103" t="n">
-        <v>-1.206</v>
+        <v>-1.2149</v>
       </c>
       <c r="E103" t="n">
-        <v>-1.9424</v>
+        <v>-1.9351</v>
       </c>
       <c r="F103" t="n">
-        <v>-1.9424</v>
+        <v>-1.9351</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>-1.9424</v>
+        <v>-1.9351</v>
       </c>
       <c r="I103" t="n">
         <v>-1.9514</v>
@@ -5188,25 +5188,25 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-2.0456</v>
+        <v>-2.0152</v>
       </c>
       <c r="C104" t="n">
-        <v>-1.4163</v>
+        <v>-1.3953</v>
       </c>
       <c r="D104" t="n">
-        <v>-1.2477</v>
+        <v>-1.2468</v>
       </c>
       <c r="E104" t="n">
-        <v>-2.0456</v>
+        <v>-2.0152</v>
       </c>
       <c r="F104" t="n">
-        <v>-2.0456</v>
+        <v>-2.0152</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.0456</v>
+        <v>-2.0152</v>
       </c>
       <c r="I104" t="n">
         <v>-2.0839</v>
@@ -5234,25 +5234,25 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-2.2687</v>
+        <v>-2.2019</v>
       </c>
       <c r="C105" t="n">
-        <v>-1.5708</v>
+        <v>-1.5245</v>
       </c>
       <c r="D105" t="n">
-        <v>-1.3379</v>
+        <v>-1.3211</v>
       </c>
       <c r="E105" t="n">
-        <v>-2.2687</v>
+        <v>-2.2019</v>
       </c>
       <c r="F105" t="n">
-        <v>-2.2687</v>
+        <v>-2.2019</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>-2.2687</v>
+        <v>-2.2019</v>
       </c>
       <c r="I105" t="n">
         <v>-2.3546</v>
@@ -5280,25 +5280,25 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-2.3525</v>
+        <v>-2.3004</v>
       </c>
       <c r="C106" t="n">
-        <v>-1.6288</v>
+        <v>-1.5927</v>
       </c>
       <c r="D106" t="n">
-        <v>-1.3717</v>
+        <v>-1.3604</v>
       </c>
       <c r="E106" t="n">
-        <v>-2.3525</v>
+        <v>-2.3004</v>
       </c>
       <c r="F106" t="n">
-        <v>-2.3525</v>
+        <v>-2.3004</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>-2.3525</v>
+        <v>-2.3004</v>
       </c>
       <c r="I106" t="n">
         <v>-2.419</v>
@@ -5322,93 +5322,93 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>junior</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-2.3645</v>
+        <v>-2.3137</v>
       </c>
       <c r="C107" t="n">
-        <v>-1.6371</v>
+        <v>-1.6019</v>
       </c>
       <c r="D107" t="n">
-        <v>-1.3766</v>
+        <v>-1.3657</v>
       </c>
       <c r="E107" t="n">
-        <v>-2.3645</v>
+        <v>-2.3137</v>
       </c>
       <c r="F107" t="n">
-        <v>-2.3645</v>
+        <v>-2.3137</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>-2.3645</v>
+        <v>-2.3137</v>
       </c>
       <c r="I107" t="n">
-        <v>-2.3645</v>
+        <v>-2.4741</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>229</v>
+        <v>350</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>-2.3645</v>
+        <v>-2.4741</v>
       </c>
       <c r="N107" t="n">
-        <v>229</v>
+        <v>350</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-2.3839</v>
+        <v>-2.3645</v>
       </c>
       <c r="C108" t="n">
-        <v>-1.6505</v>
+        <v>-1.6371</v>
       </c>
       <c r="D108" t="n">
-        <v>-1.3844</v>
+        <v>-1.3859</v>
       </c>
       <c r="E108" t="n">
-        <v>-2.3839</v>
+        <v>-2.3645</v>
       </c>
       <c r="F108" t="n">
-        <v>-2.3839</v>
+        <v>-2.3645</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>-2.3839</v>
+        <v>-2.3645</v>
       </c>
       <c r="I108" t="n">
-        <v>-2.4741</v>
+        <v>-2.3645</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>350</v>
+        <v>229</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>-2.4741</v>
+        <v>-2.3645</v>
       </c>
       <c r="N108" t="n">
-        <v>350</v>
+        <v>229</v>
       </c>
     </row>
     <row r="109">
@@ -5418,25 +5418,25 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-2.4005</v>
+        <v>-2.3738</v>
       </c>
       <c r="C109" t="n">
-        <v>-1.662</v>
+        <v>-1.6435</v>
       </c>
       <c r="D109" t="n">
-        <v>-1.3911</v>
+        <v>-1.3896</v>
       </c>
       <c r="E109" t="n">
-        <v>-2.4005</v>
+        <v>-2.3738</v>
       </c>
       <c r="F109" t="n">
-        <v>-2.4005</v>
+        <v>-2.3738</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>-2.4005</v>
+        <v>-2.3738</v>
       </c>
       <c r="I109" t="n">
         <v>-2.4342</v>
@@ -5470,7 +5470,7 @@
         <v>-1.6633</v>
       </c>
       <c r="D110" t="n">
-        <v>-1.3919</v>
+        <v>-1.401</v>
       </c>
       <c r="E110" t="n">
         <v>-2.4024</v>
@@ -5506,93 +5506,93 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>prt</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-2.7704</v>
+        <v>-2.764</v>
       </c>
       <c r="C111" t="n">
-        <v>-1.9181</v>
+        <v>-1.9137</v>
       </c>
       <c r="D111" t="n">
-        <v>-1.5405</v>
+        <v>-1.5451</v>
       </c>
       <c r="E111" t="n">
-        <v>-2.7704</v>
+        <v>-2.764</v>
       </c>
       <c r="F111" t="n">
-        <v>-2.7704</v>
+        <v>-2.764</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>-2.7704</v>
+        <v>-2.764</v>
       </c>
       <c r="I111" t="n">
-        <v>-2.7704</v>
+        <v>-3.0056</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>278</v>
+        <v>457</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>-2.7704</v>
+        <v>-3.0056</v>
       </c>
       <c r="N111" t="n">
-        <v>278</v>
+        <v>457</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>prt</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-2.8692</v>
+        <v>-2.7704</v>
       </c>
       <c r="C112" t="n">
-        <v>-1.9865</v>
+        <v>-1.9181</v>
       </c>
       <c r="D112" t="n">
-        <v>-1.5805</v>
+        <v>-1.5476</v>
       </c>
       <c r="E112" t="n">
-        <v>-2.8692</v>
+        <v>-2.7704</v>
       </c>
       <c r="F112" t="n">
-        <v>-2.8692</v>
+        <v>-2.7704</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>-2.8692</v>
+        <v>-2.7704</v>
       </c>
       <c r="I112" t="n">
-        <v>-3.0056</v>
+        <v>-2.7704</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>457</v>
+        <v>278</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>-3.0056</v>
+        <v>-2.7704</v>
       </c>
       <c r="N112" t="n">
-        <v>457</v>
+        <v>278</v>
       </c>
     </row>
     <row r="113">
@@ -5602,25 +5602,25 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-2.95</v>
+        <v>-2.9171</v>
       </c>
       <c r="C113" t="n">
-        <v>-2.0425</v>
+        <v>-2.0197</v>
       </c>
       <c r="D113" t="n">
-        <v>-1.6131</v>
+        <v>-1.6061</v>
       </c>
       <c r="E113" t="n">
-        <v>-2.95</v>
+        <v>-2.9171</v>
       </c>
       <c r="F113" t="n">
-        <v>-2.95</v>
+        <v>-2.9171</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>-2.95</v>
+        <v>-2.9171</v>
       </c>
       <c r="I113" t="n">
         <v>-2.9914</v>
@@ -5648,25 +5648,25 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-3.003</v>
+        <v>-2.9584</v>
       </c>
       <c r="C114" t="n">
-        <v>-2.0792</v>
+        <v>-2.0483</v>
       </c>
       <c r="D114" t="n">
-        <v>-1.6345</v>
+        <v>-1.6225</v>
       </c>
       <c r="E114" t="n">
-        <v>-3.003</v>
+        <v>-2.9584</v>
       </c>
       <c r="F114" t="n">
-        <v>-3.003</v>
+        <v>-2.9584</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>-3.003</v>
+        <v>-2.9584</v>
       </c>
       <c r="I114" t="n">
         <v>-3.0593</v>
@@ -5690,93 +5690,93 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Jonji</t>
+          <t>almazer</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-3.2762</v>
+        <v>-3.1724</v>
       </c>
       <c r="C115" t="n">
-        <v>-2.2683</v>
+        <v>-2.1965</v>
       </c>
       <c r="D115" t="n">
-        <v>-1.7449</v>
+        <v>-1.7078</v>
       </c>
       <c r="E115" t="n">
-        <v>-3.2762</v>
+        <v>-3.1724</v>
       </c>
       <c r="F115" t="n">
-        <v>-3.2762</v>
+        <v>-3.1724</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>-3.2762</v>
+        <v>-3.1724</v>
       </c>
       <c r="I115" t="n">
-        <v>-3.2762</v>
+        <v>-3.4209</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>229</v>
+        <v>441</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>-3.2762</v>
+        <v>-3.4209</v>
       </c>
       <c r="N115" t="n">
-        <v>229</v>
+        <v>441</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>almazer</t>
+          <t>Jonji</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-3.2809</v>
+        <v>-3.2762</v>
       </c>
       <c r="C116" t="n">
-        <v>-2.2716</v>
+        <v>-2.2683</v>
       </c>
       <c r="D116" t="n">
-        <v>-1.7468</v>
+        <v>-1.7491</v>
       </c>
       <c r="E116" t="n">
-        <v>-3.2809</v>
+        <v>-3.2762</v>
       </c>
       <c r="F116" t="n">
-        <v>-3.2809</v>
+        <v>-3.2762</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>-3.2809</v>
+        <v>-3.2762</v>
       </c>
       <c r="I116" t="n">
-        <v>-3.4209</v>
+        <v>-3.2762</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>441</v>
+        <v>229</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>-3.4209</v>
+        <v>-3.2762</v>
       </c>
       <c r="N116" t="n">
-        <v>441</v>
+        <v>229</v>
       </c>
     </row>
     <row r="117">
@@ -5786,25 +5786,25 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-3.3692</v>
+        <v>-3.3192</v>
       </c>
       <c r="C117" t="n">
-        <v>-2.3327</v>
+        <v>-2.2981</v>
       </c>
       <c r="D117" t="n">
-        <v>-1.7824</v>
+        <v>-1.7663</v>
       </c>
       <c r="E117" t="n">
-        <v>-3.3692</v>
+        <v>-3.3192</v>
       </c>
       <c r="F117" t="n">
-        <v>-3.3692</v>
+        <v>-3.3192</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>-3.3692</v>
+        <v>-3.3192</v>
       </c>
       <c r="I117" t="n">
         <v>-3.4324</v>
@@ -5838,7 +5838,7 @@
         <v>-2.4466</v>
       </c>
       <c r="D118" t="n">
-        <v>-1.8489</v>
+        <v>-1.8517</v>
       </c>
       <c r="E118" t="n">
         <v>-3.5337</v>
@@ -5878,25 +5878,25 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-3.6874</v>
+        <v>-3.6737</v>
       </c>
       <c r="C119" t="n">
-        <v>-2.553</v>
+        <v>-2.5436</v>
       </c>
       <c r="D119" t="n">
-        <v>-1.911</v>
+        <v>-1.9075</v>
       </c>
       <c r="E119" t="n">
-        <v>-3.6874</v>
+        <v>-3.6737</v>
       </c>
       <c r="F119" t="n">
-        <v>-3.6874</v>
+        <v>-3.6737</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>-3.6874</v>
+        <v>-3.6737</v>
       </c>
       <c r="I119" t="n">
         <v>-3.7046</v>
@@ -5930,7 +5930,7 @@
         <v>-3.3017</v>
       </c>
       <c r="D120" t="n">
-        <v>-2.3478</v>
+        <v>-2.3438</v>
       </c>
       <c r="E120" t="n">
         <v>-4.7687</v>
@@ -5970,25 +5970,25 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-5.1743</v>
+        <v>-5.0785</v>
       </c>
       <c r="C121" t="n">
-        <v>-3.5825</v>
+        <v>-3.5162</v>
       </c>
       <c r="D121" t="n">
-        <v>-2.5117</v>
+        <v>-2.4672</v>
       </c>
       <c r="E121" t="n">
-        <v>-5.1743</v>
+        <v>-5.0785</v>
       </c>
       <c r="F121" t="n">
-        <v>-5.1743</v>
+        <v>-5.0785</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>-5.1743</v>
+        <v>-5.0785</v>
       </c>
       <c r="I121" t="n">
         <v>-5.2958</v>
